--- a/output/laminas_comunales/comunal_o_ocup_a_2021_nuble.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,121 +375,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C2">
-        <v>36.8605463564592</v>
+        <v>57.2628038563345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.2316289712224</v>
+        <v>54.9774809753067</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="C4">
-        <v>32.3586941858897</v>
+        <v>54.1153264159101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="C5">
-        <v>32.0272854306097</v>
+        <v>53.9323614003769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="C6">
-        <v>31.7414668394902</v>
+        <v>51.240676993689</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="C7">
-        <v>31.2766577679585</v>
+        <v>50.624064886999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="C8">
-        <v>30.7661727635127</v>
+        <v>50.3189950013155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C9">
-        <v>30.2007765403086</v>
+        <v>50.0219463255581</v>
       </c>
     </row>
     <row r="10">
@@ -504,112 +504,112 @@
         </is>
       </c>
       <c r="C10">
-        <v>30.1905829596413</v>
+        <v>49.7868999551368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="C11">
-        <v>29.8003680407862</v>
+        <v>48.465954077593</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C12">
-        <v>28.447695930037</v>
+        <v>45.5442511476994</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="C13">
-        <v>25.597927185756</v>
+        <v>44.914894905809</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C14">
-        <v>25.5934198803615</v>
+        <v>43.9001316222442</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C15">
-        <v>25.5097148624779</v>
+        <v>43.7769925402434</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C16">
-        <v>25.2538759689922</v>
+        <v>43.7307334380271</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C17">
-        <v>25.0384319754035</v>
+        <v>43.5694769711163</v>
       </c>
     </row>
     <row r="18">
@@ -624,37 +624,1747 @@
         </is>
       </c>
       <c r="C18">
-        <v>24.4317236502787</v>
+        <v>42.5471264367816</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C19">
-        <v>22.8577595510468</v>
+        <v>42.281631557762</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>42.1142080217539</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>41.9116220411331</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>41.8984240497947</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>41.8078672464637</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>41.7834479111581</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>41.3793499747161</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>41.0327635327635</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>40.524625267666</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>40.2413431269675</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>40.0946378105013</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>39.9695585996956</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>38.6103663985702</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>38.0839895013123</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>37.7906807532233</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>37.3645961881256</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>16202</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Cobquecura</t>
         </is>
       </c>
-      <c r="C20">
+      <c r="C35">
+        <v>37.3188405797101</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>37.047619047619</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>36.9356819747761</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>36.8605463564592</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>36.8514632155765</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>36.544502617801</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>36.2316289712224</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>36.1310529279279</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>34.8053599374022</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>34.4327371465675</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>33.3794466403162</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>33.3474315595201</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>32.3947836395969</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>32.3586941858897</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>32.3419203747073</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>32.0272854306097</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>31.7414668394902</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>31.5529983532152</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>31.436575732525</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>31.3809523809524</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>31.2766577679585</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>31.1527325370974</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>30.8987368719841</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>30.8234851118063</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>30.8174421561149</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>30.8156283759453</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>30.7661727635127</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>30.7451151939341</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>30.7448229792919</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>30.7180650037793</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>30.6773618538324</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>30.6448157669237</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>30.506468705452</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>30.3100775193798</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>30.2582596556538</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>30.2007765403086</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>30.1905829596413</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>30.1131336114271</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>29.8003680407862</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>29.7966862707899</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>29.6428571428571</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>29.3522135416667</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>29.2967348403301</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>29.0116497557309</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>28.850723698423</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>28.7684729064039</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>28.7140889413617</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>28.447695930037</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>28.2714660667417</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>28.1573986804901</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>27.5014417531719</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>26.893470790378</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>25.8634595312648</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>25.6388888888889</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>25.597927185756</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>25.5934198803615</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>25.5097148624779</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>25.2538759689922</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>25.0790826413602</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>25.0384319754035</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>24.9470630584847</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>24.6403352471458</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>24.4317236502787</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>23.9024986041318</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>23.7238723872387</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>23.4877246266768</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>22.985305491106</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>22.8577595510468</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>22.6123460354119</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>22.5642544659132</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C105">
         <v>21.5675057208238</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>21.4888430526908</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>21.336855587576</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>20.7562408223201</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>20.5802077830604</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>20.2817430503381</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>20.1881113619263</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>19.5321353407803</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>18.2640492686682</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>18.2320838718943</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>17.4197793933317</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>9.04789872096058</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>8.925357331921649</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>8.905453938027231</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>8.61421284808382</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>7.74039345467917</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>7.63321995464853</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>7.62111004170677</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>7.52677240070489</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>7.42434904996481</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>7.15689675106949</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>6.71482075976458</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>6.50592007893438</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>6.22483028420205</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>5.76020408163265</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>5.42285916489738</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>5.20833333333333</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>4.94250850639446</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>4.78888888888889</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>4.39706862091939</v>
       </c>
     </row>
   </sheetData>
